--- a/data/trending_integrated_20260908_12.xlsx
+++ b/data/trending_integrated_20260908_12.xlsx
@@ -578,13 +578,13 @@
         <v>-0.35</v>
       </c>
       <c r="E2" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F2" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G2" t="n">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="H2" t="n">
         <v>0.45</v>
@@ -610,7 +610,7 @@
         <v>0.8</v>
       </c>
       <c r="O2" t="n">
-        <v>141690531343</v>
+        <v>141766964063</v>
       </c>
       <c r="P2" t="n">
         <v>8100</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>AI 데이터센터 국산화 사업 수행 기관 선정 및 광통신 상용화 기대감. 정부 주도 사업 선정으로 인한 급등세 및 추가 상승 가능성.</t>
+          <t>AI 데이터센터 정부 주최 국산화 수행기관 선정 및 광통신 사업 성장 기대감. 30% 급등 기록.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['AI 데이터센터', '광통신', '국산화']</t>
+          <t>['AI 데이터센터', '국산화', '광통신']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10260</v>
+        <v>10240</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+21.85%</t>
+          <t>+21.62%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G3" t="n">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H3" t="n">
         <v>0.62</v>
@@ -702,7 +702,7 @@
         <v>0.6</v>
       </c>
       <c r="O3" t="n">
-        <v>268222900480</v>
+        <v>269491521400</v>
       </c>
       <c r="P3" t="n">
         <v>15960</v>
@@ -718,12 +718,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미프진 국내 독점 판권 보유 기업으로서, 연내 허가 기대감 및 정부 지원 가능성에 따른 급등세. 전략적 투자 유치 및 탈모 이슈와 함께 제2의 삼천당제약으로 거론.</t>
+          <t>미프진 국내 독점 판권 보유 및 연내 허가 기대감. 탈모 이슈와 함께 복합적 재료 보유.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>36400</v>
+        <v>36450</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+19.15%</t>
+          <t>+19.31%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>579</v>
+        <v>590</v>
       </c>
       <c r="F4" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="G4" t="n">
-        <v>996</v>
+        <v>1044</v>
       </c>
       <c r="H4" t="n">
         <v>0.23</v>
@@ -794,7 +794,7 @@
         <v>0.16</v>
       </c>
       <c r="O4" t="n">
-        <v>774664933225</v>
+        <v>783789631625</v>
       </c>
       <c r="P4" t="n">
         <v>39350</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>정부 지분 공시(6.54%) 및 차세대 기술 보유 부각, 주포 세력의 강한 매집 의지 확인. 10만원 돌파 기대.</t>
+          <t>정부 지분 공시 및 비교군 없는 세계 최초 기술 보유. 주포의 강한 상승 의지 표출.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['정부 지분', '차세대 기술', '주포']</t>
+          <t>['정부 지분', '세계 최초 기술', '주포']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>143200</v>
+        <v>143300</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+17.09%</t>
+          <t>+17.17%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.11</v>
       </c>
       <c r="E5" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F5" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G5" t="n">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="H5" t="n">
         <v>13.33</v>
@@ -886,7 +886,7 @@
         <v>13.22</v>
       </c>
       <c r="O5" t="n">
-        <v>186998260600</v>
+        <v>191185813200</v>
       </c>
       <c r="P5" t="n">
         <v>198000</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>260조 원전 사업 관련 뉴스 기반 단기적 고점 논란. 미국 원전 수주 구체적 내용 및 외인 매도세 주목.</t>
+          <t>260조 규모의 미국 원전 사업 관련 뉴스와 구체적인 내용 언급이 있으나, 단기적 고점 및 재료 소멸 우려와 외인 매도세가 관찰됩니다.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['원전 사업', '260조', '외인']</t>
+          <t>['원전 사업', '260조', '외인 매도']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20800</v>
+        <v>20650</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+12.98%</t>
+          <t>+12.17%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F6" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="G6" t="n">
-        <v>1079</v>
+        <v>1086</v>
       </c>
       <c r="H6" t="n">
         <v>10.47</v>
@@ -978,7 +978,7 @@
         <v>10.4</v>
       </c>
       <c r="O6" t="n">
-        <v>407327081865</v>
+        <v>419577119365</v>
       </c>
       <c r="P6" t="n">
         <v>40350</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>원전 사업 수주 및 신사업 재료 발표 기대감으로 인한 급등세. 미국 원전 건설 및 에너지 인프라 건설 관련 호재가 부각되며 2만 돌파.</t>
+          <t>원전 사업 신사업 재료 발표 임박 및 에너지 인프라 건설 수요 증가 전망. 2만 원 돌파 기록.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12110</v>
+        <v>12020</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+10.90%</t>
+          <t>+10.07%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.11</v>
       </c>
       <c r="E7" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F7" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G7" t="n">
-        <v>398</v>
+        <v>411</v>
       </c>
       <c r="H7" t="n">
         <v>5.42</v>
@@ -1070,7 +1070,7 @@
         <v>5.53</v>
       </c>
       <c r="O7" t="n">
-        <v>121111478900</v>
+        <v>122724730790</v>
       </c>
       <c r="P7" t="n">
         <v>30200</v>
@@ -1086,12 +1086,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>프랑스와의 원자력 협정 및 대규모 원전 투자 기대감. 주가 상승 및 공매도 상환 압박 전망.</t>
+          <t>원전 섹터 전반의 상승 기대감과 프랑스와의 원자력 협정 소식이 있으나, 공매도 상환 및 관망 심리가 혼재합니다.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3910</v>
+        <v>3885</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+9.22%</t>
+          <t>+8.52%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.31</v>
       </c>
       <c r="E8" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F8" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G8" t="n">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="H8" t="n">
         <v>1.56</v>
@@ -1162,7 +1162,7 @@
         <v>1.25</v>
       </c>
       <c r="O8" t="n">
-        <v>249011910123</v>
+        <v>251443374892</v>
       </c>
       <c r="P8" t="n">
         <v>4335</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>탈모 치료제 관련 건보료 적용 기대감 및 신약 개발 가능성 부각. 10년 매집 후 시세 분출 가능성에 대한 기대감.</t>
+          <t>탈모 치료제 관련 이슈와 함께 10년 매집 후 주가 상승 기대감. 거래량 증가 추세.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['탈모 치료제', '건보료 적용', '신약 개발']</t>
+          <t>['탈모 치료제', '10년 매집', '거래량']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>50900</v>
+        <v>50700</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+6.04%</t>
+          <t>+5.62%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.1</v>
       </c>
       <c r="E9" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G9" t="n">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="H9" t="n">
         <v>38.34</v>
@@ -1254,7 +1254,7 @@
         <v>38.24</v>
       </c>
       <c r="O9" t="n">
-        <v>115559988725</v>
+        <v>117433076875</v>
       </c>
       <c r="P9" t="n">
         <v>67300</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>92800</v>
+        <v>92700</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+5.57%</t>
+          <t>+5.46%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.1</v>
       </c>
       <c r="E10" t="n">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="F10" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G10" t="n">
-        <v>1947</v>
+        <v>1959</v>
       </c>
       <c r="H10" t="n">
         <v>23.63</v>
@@ -1346,7 +1346,7 @@
         <v>23.53</v>
       </c>
       <c r="O10" t="n">
-        <v>357298618100</v>
+        <v>364898887000</v>
       </c>
       <c r="P10" t="n">
         <v>139200</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1869000</v>
+        <v>1877000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+4.82%</t>
+          <t>+5.27%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.13</v>
       </c>
       <c r="E11" t="n">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="F11" t="n">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="G11" t="n">
-        <v>2318</v>
+        <v>2320</v>
       </c>
       <c r="H11" t="n">
         <v>50.63</v>
@@ -1429,7 +1429,7 @@
         <v>1799000</v>
       </c>
       <c r="L11" t="n">
-        <v>1870000</v>
+        <v>1878000</v>
       </c>
       <c r="M11" t="n">
         <v>1777000</v>
@@ -1438,7 +1438,7 @@
         <v>50.5</v>
       </c>
       <c r="O11" t="n">
-        <v>3885814059000</v>
+        <v>4047769922500</v>
       </c>
       <c r="P11" t="n">
         <v>2987000</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>반도체 업황 개선 및 낸드메모리 품귀 현상으로 인한 4거래일 만 19% 상승. 용인 반도체 클러스터 구축 및 40조 자사주 매입 계획은 향후 추가 상승 기대감.</t>
+          <t>반도체 업황 개선 및 낸드메모리 품귀 현상 전망. 40조 자사주 매수 및 400만 원 목표 주가 제시.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['낸드메모리', '자사주 매입', '반도체 클러스터']</t>
+          <t>['낸드메모리', '자사주 매수', '반도체']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13990</v>
+        <v>13980</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+3.86%</t>
+          <t>+3.79%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.12</v>
       </c>
       <c r="E12" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F12" t="n">
         <v>81</v>
       </c>
       <c r="G12" t="n">
-        <v>513</v>
+        <v>525</v>
       </c>
       <c r="H12" t="n">
         <v>1.94</v>
@@ -1530,7 +1530,7 @@
         <v>1.82</v>
       </c>
       <c r="O12" t="n">
-        <v>195448208715</v>
+        <v>196527939310</v>
       </c>
       <c r="P12" t="n">
         <v>31500</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>Texas 관련 소식 및 차트 분석 기반 단기 저항선 돌파 기대감. 투경 판단일 변동성 주시.</t>
+          <t>Texas 소식과 함께 광통신 사업 성장 기대감. 투경 재지정 판단 및 공매도 물량 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['Texas', '매물대', '차트']</t>
+          <t>['Texas', '광통신', '투경']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>34000</v>
+        <v>33950</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+3.82%</t>
+          <t>+3.66%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.01</v>
       </c>
       <c r="E13" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F13" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G13" t="n">
-        <v>302</v>
+        <v>324</v>
       </c>
       <c r="H13" t="n">
         <v>52.7</v>
@@ -1622,7 +1622,7 @@
         <v>21.02</v>
       </c>
       <c r="O13" t="n">
-        <v>64856933425</v>
+        <v>65558705250</v>
       </c>
       <c r="P13" t="n">
         <v>69500</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미국 원전 사업 투자 기대감으로 인한 주가 상승. 공매도 세력과의 공방.</t>
+          <t>미국 웨스팅하우스 지분 인수 추진 및 원전 사업 확대 기대감. 공매도 물량 집중에도 반등 시도.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['원전', '투자', '공매도']</t>
+          <t>['웨스팅하우스', '원전', '지분 인수']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>277500</v>
+        <v>278500</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+2.78%</t>
+          <t>+3.15%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.06</v>
       </c>
       <c r="E14" t="n">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="F14" t="n">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="G14" t="n">
-        <v>1872</v>
+        <v>1838</v>
       </c>
       <c r="H14" t="n">
         <v>46.79</v>
@@ -1705,7 +1705,7 @@
         <v>272000</v>
       </c>
       <c r="L14" t="n">
-        <v>278000</v>
+        <v>278500</v>
       </c>
       <c r="M14" t="n">
         <v>269000</v>
@@ -1714,7 +1714,7 @@
         <v>46.73</v>
       </c>
       <c r="O14" t="n">
-        <v>3067860465750</v>
+        <v>3308810046000</v>
       </c>
       <c r="P14" t="n">
         <v>374500</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>공매도 압박 속 28만 돌파 시도 및 30만 전자 입성 기대감. 자사주 매수 및 배당 정책 강화, 로봇 출시 등은 긍정적 요인.</t>
+          <t>정치적 이슈와 함께 공매도 세력과의 공방 지속. 30만 전자 입성 및 자사주 매수 기대감.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['공매도', '자사주 매수', '로봇']</t>
+          <t>['공매도', '자사주 매수', '30만 전자']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10450</v>
+        <v>10520</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+2.45%</t>
+          <t>+3.14%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.23</v>
       </c>
       <c r="E15" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="F15" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G15" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H15" t="n">
         <v>0.44</v>
@@ -1806,7 +1806,7 @@
         <v>0.21</v>
       </c>
       <c r="O15" t="n">
-        <v>67888891495</v>
+        <v>72942831290</v>
       </c>
       <c r="P15" t="n">
         <v>20850</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>터빈블레이드 수주 기대감 속 기관/외인 매수세 유입 전망. 대주주 물량 매도 후 변동성 예상.</t>
+          <t>터빈블레이드 수주 기대감과 강한 재료 발생 가능성이 제기되나, 대주주 물량 매도 및 개미 털기 의혹이 존재합니다.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['터빈블레이드', '수주', '기관']</t>
+          <t>['수주', '대주주', '재료']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1851,31 +1851,31 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>원풍물산</t>
+          <t>해치텍</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>306</v>
+        <v>15040</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+2.34%</t>
+          <t>+2.66%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.05</v>
+        <v>0.14</v>
       </c>
       <c r="E16" t="n">
-        <v>87</v>
+        <v>49</v>
       </c>
       <c r="F16" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="G16" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H16" t="n">
-        <v>5.34</v>
+        <v>1.72</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,91 +1883,91 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>299</v>
+        <v>14650</v>
       </c>
       <c r="K16" t="n">
-        <v>220</v>
+        <v>15100</v>
       </c>
       <c r="L16" t="n">
-        <v>349</v>
+        <v>16680</v>
       </c>
       <c r="M16" t="n">
-        <v>220</v>
+        <v>14800</v>
       </c>
       <c r="N16" t="n">
-        <v>5.29</v>
+        <v>1.58</v>
       </c>
       <c r="O16" t="n">
-        <v>8008445856</v>
+        <v>45861196040</v>
       </c>
       <c r="P16" t="n">
-        <v>901</v>
+        <v>21400</v>
       </c>
       <c r="Q16" t="n">
-        <v>217</v>
+        <v>12090</v>
       </c>
       <c r="R16" t="n">
-        <v>727000</v>
+        <v>-3000</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>상장폐지 가능성 및 정리매매 돌입에 대한 우려. 대규모 거래량 발생 및 변동성 확대 속에 투자 주의 요구.</t>
+          <t>단주 거래 및 자전거래 의혹과 함께 스카이랩스 대비 낮은 평가.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['상장폐지', '정리매매', '거래량']</t>
+          <t>['단주 거래', '자전거래', '스카이랩스']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>008290</t>
+          <t>0155E0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>해치텍</t>
+          <t>원풍물산</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>14970</v>
+        <v>300</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+2.18%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.14</v>
+        <v>0.05</v>
       </c>
       <c r="E17" t="n">
-        <v>47</v>
+        <v>89</v>
       </c>
       <c r="F17" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="G17" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="H17" t="n">
-        <v>1.72</v>
+        <v>5.34</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,60 +1975,60 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>14650</v>
+        <v>299</v>
       </c>
       <c r="K17" t="n">
-        <v>15100</v>
+        <v>220</v>
       </c>
       <c r="L17" t="n">
-        <v>16680</v>
+        <v>349</v>
       </c>
       <c r="M17" t="n">
-        <v>14800</v>
+        <v>220</v>
       </c>
       <c r="N17" t="n">
-        <v>1.58</v>
+        <v>5.29</v>
       </c>
       <c r="O17" t="n">
-        <v>45582431950</v>
+        <v>8192145524</v>
       </c>
       <c r="P17" t="n">
-        <v>21400</v>
+        <v>901</v>
       </c>
       <c r="Q17" t="n">
-        <v>12090</v>
+        <v>217</v>
       </c>
       <c r="R17" t="n">
-        <v>-3000</v>
+        <v>727000</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>단주 거래 및 자전거래 의혹과 함께 스카이랩스 대비 낮은 평가.</t>
+          <t>상장폐지 가능성 언급 속 변동성 확대. 정리매매 및 종가 하락 우려.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['단주 거래', '자전거래', '스카이랩스']</t>
+          <t>['상장폐지', '정리매매', '변동성']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>0155E0</t>
+          <t>008290</t>
         </is>
       </c>
     </row>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>15730</v>
+        <v>16070</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-2.36%</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="F18" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G18" t="n">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -2082,7 +2082,7 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>36651884795</v>
+        <v>41184091345</v>
       </c>
       <c r="P18" t="n">
         <v>19380</v>
@@ -2127,70 +2127,70 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>삼익제약</t>
+          <t>금호전기</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8530</v>
+        <v>12370</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.85%</t>
+          <t>-2.44%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.04</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F19" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G19" t="n">
-        <v>44</v>
+        <v>130</v>
       </c>
       <c r="H19" t="n">
-        <v>1.68</v>
+        <v>17.11</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>8780</v>
+        <v>12680</v>
       </c>
       <c r="K19" t="n">
-        <v>9060</v>
+        <v>12680</v>
       </c>
       <c r="L19" t="n">
-        <v>9960</v>
+        <v>12680</v>
       </c>
       <c r="M19" t="n">
-        <v>8270</v>
+        <v>11550</v>
       </c>
       <c r="N19" t="n">
-        <v>1.72</v>
+        <v>18.05</v>
       </c>
       <c r="O19" t="n">
-        <v>106143746645</v>
+        <v>29297294100</v>
       </c>
       <c r="P19" t="n">
-        <v>25050</v>
+        <v>14350</v>
       </c>
       <c r="Q19" t="n">
-        <v>3705</v>
+        <v>465</v>
       </c>
       <c r="R19" t="n">
-        <v>-59000</v>
+        <v>48000</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>투경 지정 가능성 및 탈모 테마 관련 언급, 급등 후 조정 가능성 시사.</t>
+          <t>계단식 하락 및 하한가 가능성 언급. 투자자들의 공포 심리 확산.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['투경', '탈모 테마', 'JAK 억제']</t>
+          <t>['하락', '하한가', '공포']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,77 +2212,77 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>014950</t>
+          <t>001210</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>금호전기</t>
+          <t>삼익제약</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>12140</v>
+        <v>8430</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-4.26%</t>
+          <t>-3.99%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.04</v>
       </c>
       <c r="E20" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F20" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G20" t="n">
-        <v>129</v>
+        <v>45</v>
       </c>
       <c r="H20" t="n">
-        <v>17.11</v>
+        <v>1.68</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>12680</v>
+        <v>8780</v>
       </c>
       <c r="K20" t="n">
-        <v>12680</v>
+        <v>9060</v>
       </c>
       <c r="L20" t="n">
-        <v>12680</v>
+        <v>9960</v>
       </c>
       <c r="M20" t="n">
-        <v>11550</v>
+        <v>8270</v>
       </c>
       <c r="N20" t="n">
-        <v>18.05</v>
+        <v>1.72</v>
       </c>
       <c r="O20" t="n">
-        <v>27233477290</v>
+        <v>106990736255</v>
       </c>
       <c r="P20" t="n">
-        <v>14350</v>
+        <v>25050</v>
       </c>
       <c r="Q20" t="n">
-        <v>465</v>
+        <v>3705</v>
       </c>
       <c r="R20" t="n">
-        <v>48000</v>
+        <v>-59000</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>계단식 하락 및 하한가 가능성 언급. 투자자들의 공포 심리 확산.</t>
+          <t>투경 지정 가능성 및 탈모 테마 관련 언급, 급등 후 조정 가능성 시사.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,11 +2291,11 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['하락', '하한가', '공포']</t>
+          <t>['투경', '탈모 테마', 'JAK 억제']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>001210</t>
+          <t>014950</t>
         </is>
       </c>
     </row>
@@ -2326,13 +2326,13 @@
         <v>0.15</v>
       </c>
       <c r="E21" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F21" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G21" t="n">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="H21" t="n">
         <v>38.84</v>
@@ -2358,7 +2358,7 @@
         <v>38.69</v>
       </c>
       <c r="O21" t="n">
-        <v>28545078540</v>
+        <v>28978939025</v>
       </c>
       <c r="P21" t="n">
         <v>19150</v>
@@ -2407,11 +2407,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-93.01%</t>
+          <t>-92.98%</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -2424,7 +2424,7 @@
         <v>52</v>
       </c>
       <c r="G22" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H22" t="n">
         <v>0.08</v>
@@ -2450,7 +2450,7 @@
         <v>0.08</v>
       </c>
       <c r="O22" t="n">
-        <v>863046022</v>
+        <v>897092097</v>
       </c>
       <c r="P22" t="n">
         <v>3660</v>

--- a/data/trending_integrated_20260908_12.xlsx
+++ b/data/trending_integrated_20260908_12.xlsx
@@ -578,13 +578,13 @@
         <v>-0.35</v>
       </c>
       <c r="E2" t="n">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="F2" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="G2" t="n">
-        <v>217</v>
+        <v>247</v>
       </c>
       <c r="H2" t="n">
         <v>0.45</v>
@@ -610,7 +610,7 @@
         <v>0.8</v>
       </c>
       <c r="O2" t="n">
-        <v>141766964063</v>
+        <v>141941767783</v>
       </c>
       <c r="P2" t="n">
         <v>8100</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>AI 데이터센터 정부 주최 국산화 수행기관 선정 및 광통신 사업 성장 기대감. 30% 급등 기록.</t>
+          <t>빛과전자, AI 데이터센터 국산화 수행기관 선정 및 광통신 상용화 기대. 10방 뉴스 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['AI 데이터센터', '국산화', '광통신']</t>
+          <t>['빛과전자', 'AI 데이터센터', '광통신']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10240</v>
+        <v>10320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+21.62%</t>
+          <t>+22.57%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="F3" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G3" t="n">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="H3" t="n">
         <v>0.62</v>
@@ -702,7 +702,7 @@
         <v>0.6</v>
       </c>
       <c r="O3" t="n">
-        <v>269491521400</v>
+        <v>274126572370</v>
       </c>
       <c r="P3" t="n">
         <v>15960</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미프진 국내 독점 판권 보유 및 연내 허가 기대감. 탈모 이슈와 함께 복합적 재료 보유.</t>
+          <t>미프진 국내 독점 판권 보유 현대약품, 연내 허가 기대감. 정부 지원 및 전략적 투자 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['미프진', '독점 판권', '탈모']</t>
+          <t>['미프진', '현대약품', '독점 판권']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>36450</v>
+        <v>36900</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+19.31%</t>
+          <t>+20.79%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>590</v>
+        <v>622</v>
       </c>
       <c r="F4" t="n">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="G4" t="n">
-        <v>1044</v>
+        <v>1147</v>
       </c>
       <c r="H4" t="n">
         <v>0.23</v>
@@ -794,7 +794,7 @@
         <v>0.16</v>
       </c>
       <c r="O4" t="n">
-        <v>783789631625</v>
+        <v>804827269225</v>
       </c>
       <c r="P4" t="n">
         <v>39350</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>정부 지분 공시 및 비교군 없는 세계 최초 기술 보유. 주포의 강한 상승 의지 표출.</t>
+          <t>정부 지분 공시 및 비교군 없는 세계 첫 기술 보유, 주포 언급 및 급등 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['정부 지분', '세계 최초 기술', '주포']</t>
+          <t>['정부 지분', '세계 최초', '주포']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>143300</v>
+        <v>141300</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+17.17%</t>
+          <t>+15.54%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.11</v>
       </c>
       <c r="E5" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="F5" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="G5" t="n">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="H5" t="n">
         <v>13.33</v>
@@ -886,7 +886,7 @@
         <v>13.22</v>
       </c>
       <c r="O5" t="n">
-        <v>191185813200</v>
+        <v>199526246100</v>
       </c>
       <c r="P5" t="n">
         <v>198000</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>260조 규모의 미국 원전 사업 관련 뉴스와 구체적인 내용 언급이 있으나, 단기적 고점 및 재료 소멸 우려와 외인 매도세가 관찰됩니다.</t>
+          <t>미국 260조 원전 사업 수주 구체화 및 AP1000 계약 관련 기대감. 대형 원전 사업 관련 내용 포함.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['원전 사업', '260조', '외인 매도']</t>
+          <t>['원전', '사업', '계약']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20650</v>
+        <v>20800</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+12.17%</t>
+          <t>+12.98%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="F6" t="n">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="G6" t="n">
-        <v>1086</v>
+        <v>1117</v>
       </c>
       <c r="H6" t="n">
         <v>10.47</v>
@@ -978,7 +978,7 @@
         <v>10.4</v>
       </c>
       <c r="O6" t="n">
-        <v>419577119365</v>
+        <v>431887965915</v>
       </c>
       <c r="P6" t="n">
         <v>40350</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12020</v>
+        <v>11980</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+10.07%</t>
+          <t>+9.71%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.11</v>
       </c>
       <c r="E7" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F7" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="G7" t="n">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="H7" t="n">
         <v>5.42</v>
@@ -1070,7 +1070,7 @@
         <v>5.53</v>
       </c>
       <c r="O7" t="n">
-        <v>122724730790</v>
+        <v>126157464270</v>
       </c>
       <c r="P7" t="n">
         <v>30200</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>원전 섹터 전반의 상승 기대감과 프랑스와의 원자력 협정 소식이 있으나, 공매도 상환 및 관망 심리가 혼재합니다.</t>
+          <t>프랑스 원자력 협정 및 미국 원전 8기 수주 기대감에 따른 주가 상승 전망. 다만, 과도한 테마 열기 가능성 경계.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['원전', '협정', '공매도']</t>
+          <t>['원전', '협정', '기대감']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3885</v>
+        <v>3875</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+8.52%</t>
+          <t>+8.24%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.31</v>
       </c>
       <c r="E8" t="n">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="F8" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="G8" t="n">
-        <v>246</v>
+        <v>267</v>
       </c>
       <c r="H8" t="n">
         <v>1.56</v>
@@ -1162,7 +1162,7 @@
         <v>1.25</v>
       </c>
       <c r="O8" t="n">
-        <v>251443374892</v>
+        <v>257292170977</v>
       </c>
       <c r="P8" t="n">
         <v>4335</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>탈모 치료제 관련 이슈와 함께 10년 매집 후 주가 상승 기대감. 거래량 증가 추세.</t>
+          <t>JW신약, 탈모 관련 사업 기대감. 10년 매집 언급 및 목표가 30만 제시.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['탈모 치료제', '10년 매집', '거래량']</t>
+          <t>['JW신약', '탈모', '10년 매집']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>50700</v>
+        <v>1884000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+5.62%</t>
+          <t>+5.66%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="E9" t="n">
-        <v>72</v>
+        <v>798</v>
       </c>
       <c r="F9" t="n">
-        <v>46</v>
+        <v>486</v>
       </c>
       <c r="G9" t="n">
-        <v>208</v>
+        <v>2366</v>
       </c>
       <c r="H9" t="n">
-        <v>38.34</v>
+        <v>50.63</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,91 +1239,91 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>48000</v>
+        <v>1783000</v>
       </c>
       <c r="K9" t="n">
-        <v>48550</v>
+        <v>1799000</v>
       </c>
       <c r="L9" t="n">
-        <v>51600</v>
+        <v>1887000</v>
       </c>
       <c r="M9" t="n">
-        <v>48350</v>
+        <v>1777000</v>
       </c>
       <c r="N9" t="n">
-        <v>38.24</v>
+        <v>50.5</v>
       </c>
       <c r="O9" t="n">
-        <v>117433076875</v>
+        <v>4327610092000</v>
       </c>
       <c r="P9" t="n">
-        <v>67300</v>
+        <v>2987000</v>
       </c>
       <c r="Q9" t="n">
-        <v>23150</v>
+        <v>274000</v>
       </c>
       <c r="R9" t="n">
-        <v>275000</v>
+        <v>-8000</v>
       </c>
       <c r="S9" t="n">
-        <v>66000</v>
+        <v>108000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>건설주 상승세 및 원전, 재건 관련 기대감. 5만원 돌파 및 추가 상승 전망.</t>
+          <t>SK하이닉스, 185~195만대 물량 소화 후 상승 기대. 용인 반도체 클러스터 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['건설', '원전', '재건']</t>
+          <t>['SK하이닉스', '반도체 클러스터', '물량 소화']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>66</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>92700</v>
+        <v>50600</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+5.46%</t>
+          <t>+5.42%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.1</v>
       </c>
       <c r="E10" t="n">
-        <v>430</v>
+        <v>72</v>
       </c>
       <c r="F10" t="n">
-        <v>257</v>
+        <v>46</v>
       </c>
       <c r="G10" t="n">
-        <v>1959</v>
+        <v>209</v>
       </c>
       <c r="H10" t="n">
-        <v>23.63</v>
+        <v>38.34</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,91 +1331,91 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>87900</v>
+        <v>48000</v>
       </c>
       <c r="K10" t="n">
-        <v>91200</v>
+        <v>48550</v>
       </c>
       <c r="L10" t="n">
-        <v>93500</v>
+        <v>51600</v>
       </c>
       <c r="M10" t="n">
-        <v>90200</v>
+        <v>48350</v>
       </c>
       <c r="N10" t="n">
-        <v>23.53</v>
+        <v>38.24</v>
       </c>
       <c r="O10" t="n">
-        <v>364898887000</v>
+        <v>121092116825</v>
       </c>
       <c r="P10" t="n">
-        <v>139200</v>
+        <v>67300</v>
       </c>
       <c r="Q10" t="n">
-        <v>57000</v>
+        <v>23150</v>
       </c>
       <c r="R10" t="n">
-        <v>-222000</v>
+        <v>275000</v>
       </c>
       <c r="S10" t="n">
-        <v>267000</v>
+        <v>66000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>미국 텍사스 발전 사업 참여 확정 및 원전 8기 건설 수주 기대감. SMR 분야 강자로서 웨스팅하우스 지분 인수 및 체코 원전 시공 참여 가능성 부각.</t>
+          <t>건설주 상승세 및 원전, 재건 관련 기대감. 5만원 돌파 및 추가 상승 전망.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['SMR', '미국 발전 사업', '원전']</t>
+          <t>['건설', '원전', '재건']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1877000</v>
+        <v>92300</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+5.27%</t>
+          <t>+5.01%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="E11" t="n">
-        <v>798</v>
+        <v>444</v>
       </c>
       <c r="F11" t="n">
-        <v>476</v>
+        <v>262</v>
       </c>
       <c r="G11" t="n">
-        <v>2320</v>
+        <v>2033</v>
       </c>
       <c r="H11" t="n">
-        <v>50.63</v>
+        <v>23.63</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1783000</v>
+        <v>87900</v>
       </c>
       <c r="K11" t="n">
-        <v>1799000</v>
+        <v>91200</v>
       </c>
       <c r="L11" t="n">
-        <v>1878000</v>
+        <v>93500</v>
       </c>
       <c r="M11" t="n">
-        <v>1777000</v>
+        <v>90200</v>
       </c>
       <c r="N11" t="n">
-        <v>50.5</v>
+        <v>23.53</v>
       </c>
       <c r="O11" t="n">
-        <v>4047769922500</v>
+        <v>377347841300</v>
       </c>
       <c r="P11" t="n">
-        <v>2987000</v>
+        <v>139200</v>
       </c>
       <c r="Q11" t="n">
-        <v>274000</v>
+        <v>57000</v>
       </c>
       <c r="R11" t="n">
-        <v>-8000</v>
+        <v>-222000</v>
       </c>
       <c r="S11" t="n">
-        <v>108000</v>
+        <v>267000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>반도체 업황 개선 및 낸드메모리 품귀 현상 전망. 40조 자사주 매수 및 400만 원 목표 주가 제시.</t>
+          <t>미국 텍사스 발전 사업 참여 확정 및 원전 8기 건설 수주 기대감. SMR 분야 강자로서 웨스팅하우스 지분 인수 및 체코 원전 시공 참여 가능성 부각.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['낸드메모리', '자사주 매수', '반도체']</t>
+          <t>['SMR', '미국 발전 사업', '원전']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>66</v>
+        <v>10</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13980</v>
+        <v>14070</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+3.79%</t>
+          <t>+4.45%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.12</v>
       </c>
       <c r="E12" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="F12" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G12" t="n">
-        <v>525</v>
+        <v>553</v>
       </c>
       <c r="H12" t="n">
         <v>1.94</v>
@@ -1530,7 +1530,7 @@
         <v>1.82</v>
       </c>
       <c r="O12" t="n">
-        <v>196527939310</v>
+        <v>199515799545</v>
       </c>
       <c r="P12" t="n">
         <v>31500</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>Texas 소식과 함께 광통신 사업 성장 기대감. 투경 재지정 판단 및 공매도 물량 언급.</t>
+          <t>대한광통신, Texas 소식 및 단기 저항선 돌파 기대. 빛과전자와의 연관성 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['Texas', '광통신', '투경']</t>
+          <t>['대한광통신', 'Texas', '단기 저항선']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>33950</v>
+        <v>33900</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+3.66%</t>
+          <t>+3.51%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.01</v>
       </c>
       <c r="E13" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F13" t="n">
         <v>58</v>
       </c>
       <c r="G13" t="n">
-        <v>324</v>
+        <v>343</v>
       </c>
       <c r="H13" t="n">
         <v>52.7</v>
@@ -1622,7 +1622,7 @@
         <v>21.02</v>
       </c>
       <c r="O13" t="n">
-        <v>65558705250</v>
+        <v>67561681150</v>
       </c>
       <c r="P13" t="n">
         <v>69500</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미국 웨스팅하우스 지분 인수 추진 및 원전 사업 확대 기대감. 공매도 물량 집중에도 반등 시도.</t>
+          <t>한국전력, 웨스팅하우스 지분 인수 관련 기대감. 공매도 관련 언급 다수.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['웨스팅하우스', '원전', '지분 인수']</t>
+          <t>['한국전력', '웨스팅하우스', '공매도']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>278500</v>
+        <v>278250</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+3.15%</t>
+          <t>+3.06%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.06</v>
       </c>
       <c r="E14" t="n">
-        <v>797</v>
+        <v>789</v>
       </c>
       <c r="F14" t="n">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="G14" t="n">
-        <v>1838</v>
+        <v>1828</v>
       </c>
       <c r="H14" t="n">
         <v>46.79</v>
@@ -1705,7 +1705,7 @@
         <v>272000</v>
       </c>
       <c r="L14" t="n">
-        <v>278500</v>
+        <v>279000</v>
       </c>
       <c r="M14" t="n">
         <v>269000</v>
@@ -1714,7 +1714,7 @@
         <v>46.73</v>
       </c>
       <c r="O14" t="n">
-        <v>3308810046000</v>
+        <v>3434048050250</v>
       </c>
       <c r="P14" t="n">
         <v>374500</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>정치적 이슈와 함께 공매도 세력과의 공방 지속. 30만 전자 입성 및 자사주 매수 기대감.</t>
+          <t>삼성전자, 30만원 돌파 기대감 속 공매도 언급. 정치색 짙은 게시글 다수.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['공매도', '자사주 매수', '30만 전자']</t>
+          <t>['삼성전자', '공매도', '30만원']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10520</v>
+        <v>10470</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+3.14%</t>
+          <t>+2.65%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.23</v>
       </c>
       <c r="E15" t="n">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F15" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G15" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="H15" t="n">
         <v>0.44</v>
@@ -1806,7 +1806,7 @@
         <v>0.21</v>
       </c>
       <c r="O15" t="n">
-        <v>72942831290</v>
+        <v>78752095185</v>
       </c>
       <c r="P15" t="n">
         <v>20850</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>터빈블레이드 수주 기대감과 강한 재료 발생 가능성이 제기되나, 대주주 물량 매도 및 개미 털기 의혹이 존재합니다.</t>
+          <t>터빈블레이드 수주 기대감 및 개미 털기 논란. 기관+외계인 수급 주시.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['수주', '대주주', '재료']</t>
+          <t>['터빈블레이드', '수주', '기관']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,21 +1855,21 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15040</v>
+        <v>14990</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+2.66%</t>
+          <t>+2.32%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.14</v>
       </c>
       <c r="E16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F16" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G16" t="n">
         <v>50</v>
@@ -1898,7 +1898,7 @@
         <v>1.58</v>
       </c>
       <c r="O16" t="n">
-        <v>45861196040</v>
+        <v>46317093150</v>
       </c>
       <c r="P16" t="n">
         <v>21400</v>
@@ -1943,92 +1943,92 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>원풍물산</t>
+          <t>금호전기</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>300</v>
+        <v>12520</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>-1.26%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.05</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>89</v>
+        <v>51</v>
       </c>
       <c r="F17" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="G17" t="n">
-        <v>56</v>
+        <v>130</v>
       </c>
       <c r="H17" t="n">
-        <v>5.34</v>
+        <v>17.11</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>299</v>
+        <v>12680</v>
       </c>
       <c r="K17" t="n">
-        <v>220</v>
+        <v>12680</v>
       </c>
       <c r="L17" t="n">
-        <v>349</v>
+        <v>13130</v>
       </c>
       <c r="M17" t="n">
-        <v>220</v>
+        <v>11550</v>
       </c>
       <c r="N17" t="n">
-        <v>5.29</v>
+        <v>18.05</v>
       </c>
       <c r="O17" t="n">
-        <v>8192145524</v>
+        <v>43176451550</v>
       </c>
       <c r="P17" t="n">
-        <v>901</v>
+        <v>14350</v>
       </c>
       <c r="Q17" t="n">
-        <v>217</v>
+        <v>465</v>
       </c>
       <c r="R17" t="n">
-        <v>727000</v>
+        <v>48000</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>상장폐지 가능성 언급 속 변동성 확대. 정리매매 및 종가 하락 우려.</t>
+          <t>계단식 하락 및 하한가 가능성 언급. 투자자들의 공포 심리 확산.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['상장폐지', '정리매매', '변동성']</t>
+          <t>['하락', '하한가', '공포']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>008290</t>
+          <t>001210</t>
         </is>
       </c>
     </row>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>16070</v>
+        <v>15860</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.25%</t>
+          <t>-1.55%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="F18" t="n">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="G18" t="n">
-        <v>396</v>
+        <v>477</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -2073,7 +2073,7 @@
         <v>16130</v>
       </c>
       <c r="L18" t="n">
-        <v>16140</v>
+        <v>16420</v>
       </c>
       <c r="M18" t="n">
         <v>15310</v>
@@ -2082,7 +2082,7 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>41184091345</v>
+        <v>60997602570</v>
       </c>
       <c r="P18" t="n">
         <v>19380</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>건설주 상승세 속 호남 메가프로젝트 및 대미 투자 1호 가스복합발전소 수주 기대감. 광주공항 재개장 이슈도 긍정적 요인.</t>
+          <t>금호건설, 호남 메가 프로젝트 및 광주공항 재개장 관련 언급. 건설주 전반 상승세.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['건설주', '대미 투자', '광주공항']</t>
+          <t>['금호건설', '메가 프로젝트', '광주공항']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2127,70 +2127,70 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>금호전기</t>
+          <t>삼익제약</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>12370</v>
+        <v>8500</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.44%</t>
+          <t>-3.19%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.04</v>
       </c>
       <c r="E19" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F19" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G19" t="n">
-        <v>130</v>
+        <v>48</v>
       </c>
       <c r="H19" t="n">
-        <v>17.11</v>
+        <v>1.68</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>12680</v>
+        <v>8780</v>
       </c>
       <c r="K19" t="n">
-        <v>12680</v>
+        <v>9060</v>
       </c>
       <c r="L19" t="n">
-        <v>12680</v>
+        <v>9960</v>
       </c>
       <c r="M19" t="n">
-        <v>11550</v>
+        <v>8270</v>
       </c>
       <c r="N19" t="n">
-        <v>18.05</v>
+        <v>1.72</v>
       </c>
       <c r="O19" t="n">
-        <v>29297294100</v>
+        <v>108457703190</v>
       </c>
       <c r="P19" t="n">
-        <v>14350</v>
+        <v>25050</v>
       </c>
       <c r="Q19" t="n">
-        <v>465</v>
+        <v>3705</v>
       </c>
       <c r="R19" t="n">
-        <v>48000</v>
+        <v>-59000</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>계단식 하락 및 하한가 가능성 언급. 투자자들의 공포 심리 확산.</t>
+          <t>투경 지정 가능성 및 탈모 테마 관련 언급, 급등 후 조정 가능성 시사.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['하락', '하한가', '공포']</t>
+          <t>['투경', '탈모 테마', 'JAK 억제']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,38 +2212,38 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>001210</t>
+          <t>014950</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>삼익제약</t>
+          <t>원풍물산</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>8430</v>
+        <v>288</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-3.99%</t>
+          <t>-3.68%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.04</v>
+        <v>0.05</v>
       </c>
       <c r="E20" t="n">
-        <v>46</v>
+        <v>96</v>
       </c>
       <c r="F20" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="G20" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="H20" t="n">
-        <v>1.68</v>
+        <v>5.34</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,60 +2251,60 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>8780</v>
+        <v>299</v>
       </c>
       <c r="K20" t="n">
-        <v>9060</v>
+        <v>220</v>
       </c>
       <c r="L20" t="n">
-        <v>9960</v>
+        <v>349</v>
       </c>
       <c r="M20" t="n">
-        <v>8270</v>
+        <v>220</v>
       </c>
       <c r="N20" t="n">
-        <v>1.72</v>
+        <v>5.29</v>
       </c>
       <c r="O20" t="n">
-        <v>106990736255</v>
+        <v>8494931403</v>
       </c>
       <c r="P20" t="n">
-        <v>25050</v>
+        <v>901</v>
       </c>
       <c r="Q20" t="n">
-        <v>3705</v>
+        <v>217</v>
       </c>
       <c r="R20" t="n">
-        <v>-59000</v>
+        <v>727000</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>투경 지정 가능성 및 탈모 테마 관련 언급, 급등 후 조정 가능성 시사.</t>
+          <t>원풍물산, 상장폐지 가능성 및 정리매매 언급. 폭탄 돌리기 및 탈출 지능순 강조.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['투경', '탈모 테마', 'JAK 억제']</t>
+          <t>['원풍물산', '상장폐지', '정리매매']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>014950</t>
+          <t>008290</t>
         </is>
       </c>
     </row>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8240</v>
+        <v>8260</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-12.90%</t>
+          <t>-12.68%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.15</v>
       </c>
       <c r="E21" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="F21" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G21" t="n">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="H21" t="n">
         <v>38.84</v>
@@ -2358,7 +2358,7 @@
         <v>38.69</v>
       </c>
       <c r="O21" t="n">
-        <v>28978939025</v>
+        <v>29770948205</v>
       </c>
       <c r="P21" t="n">
         <v>19150</v>
@@ -2418,13 +2418,13 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F22" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G22" t="n">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="H22" t="n">
         <v>0.08</v>
@@ -2466,16 +2466,16 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>감사의견 적정 및 상반기 보고서 적정으로 인한 거래 재개 기대감. 그러나 과거 재무 악화 및 정리매매 시작으로 인한 불확실성 상존.</t>
+          <t>카프로, 감사의견 적정 및 상반기 보고서 제출. 유통물량 감소 및 공개 매수 가능성 언급.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['감사의견 적정', '정리매매', '재무']</t>
+          <t>['카프로', '감사의견', '유통물량']</t>
         </is>
       </c>
       <c r="X22" t="n">
